--- a/result_tables/model_metrics.xlsx
+++ b/result_tables/model_metrics.xlsx
@@ -487,10 +487,10 @@
         <v>0.6624080670634428</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6521357943282964</v>
+        <v>0.6560988152395788</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6698231436175635</v>
+        <v>0.6675098329884399</v>
       </c>
       <c r="E2" t="n">
         <v>0.9008319655894504</v>
@@ -521,10 +521,10 @@
         <v>0.5296453863193273</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5255729517139003</v>
+        <v>0.5206908164849308</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5341221964058988</v>
+        <v>0.5358380699753519</v>
       </c>
       <c r="E3" t="n">
         <v>0.8161639028807516</v>
@@ -555,10 +555,10 @@
         <v>0.6203277581891766</v>
       </c>
       <c r="C4" t="n">
-        <v>0.612280271289229</v>
+        <v>0.614098534706928</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6238486372370877</v>
+        <v>0.6299747200478053</v>
       </c>
       <c r="E4" t="n">
         <v>0.7436187673326164</v>
@@ -589,10 +589,10 @@
         <v>0.6792793907155239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6696229366903371</v>
+        <v>0.6736280115916488</v>
       </c>
       <c r="D5" t="n">
-        <v>0.683400137809134</v>
+        <v>0.6860778859508985</v>
       </c>
       <c r="E5" t="n">
         <v>0.9020657648989756</v>
@@ -623,10 +623,10 @@
         <v>0.6831023648620584</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6753383257017989</v>
+        <v>0.6757972558229426</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6899855327570505</v>
+        <v>0.691799210248532</v>
       </c>
       <c r="E6" t="n">
         <v>0.9023261078725451</v>
@@ -657,10 +657,10 @@
         <v>0.6651816288094966</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6570454259582219</v>
+        <v>0.6559723345554672</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6726380869051396</v>
+        <v>0.6737024489457332</v>
       </c>
       <c r="E7" t="n">
         <v>0.9003905144603543</v>
@@ -691,10 +691,10 @@
         <v>0.6330284173857466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6263234268655546</v>
+        <v>0.6232696010009271</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6405766067458935</v>
+        <v>0.6395842951052242</v>
       </c>
       <c r="E8" t="n">
         <v>0.9008319655894504</v>
@@ -725,10 +725,10 @@
         <v>0.669828227201491</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6614241749995494</v>
+        <v>0.6631569611256138</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6735628308193258</v>
+        <v>0.6742793978351065</v>
       </c>
       <c r="E9" t="n">
         <v>0.9015903559907182</v>
@@ -759,10 +759,10 @@
         <v>0.6302028437958425</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6186258382414918</v>
+        <v>0.6257320759014811</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6427765605640186</v>
+        <v>0.6378949580758786</v>
       </c>
       <c r="E10" t="n">
         <v>0.9013752900560303</v>
@@ -793,10 +793,10 @@
         <v>0.6707301248652564</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6601855981352445</v>
+        <v>0.6655104835706437</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6773829106858548</v>
+        <v>0.6813910089667197</v>
       </c>
       <c r="E11" t="n">
         <v>0.9021789574961797</v>
@@ -888,10 +888,10 @@
         <v>0.6686679498395911</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6628821321440327</v>
+        <v>0.6608720808004088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6763378937126507</v>
+        <v>0.6729369266222722</v>
       </c>
       <c r="E2" t="n">
         <v>0.88941934304902</v>
@@ -922,10 +922,10 @@
         <v>0.6487363888536324</v>
       </c>
       <c r="C3" t="n">
-        <v>0.640548682844805</v>
+        <v>0.6423390876939419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6543568267181599</v>
+        <v>0.6533269696786249</v>
       </c>
       <c r="E3" t="n">
         <v>0.8898914218709549</v>
@@ -956,10 +956,10 @@
         <v>0.6210500711356677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6122399335726678</v>
+        <v>0.6135901726554309</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6250332071600321</v>
+        <v>0.6264079834281797</v>
       </c>
       <c r="E4" t="n">
         <v>0.7312500951771819</v>
@@ -990,10 +990,10 @@
         <v>0.6848602418428751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6787413083926077</v>
+        <v>0.6790668188863594</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6903949812143733</v>
+        <v>0.6897956521172403</v>
       </c>
       <c r="E5" t="n">
         <v>0.8900893904091858</v>
@@ -1024,10 +1024,10 @@
         <v>0.6944149698602582</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6882344149000742</v>
+        <v>0.6880796451653252</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7008166789684577</v>
+        <v>0.6986629388100347</v>
       </c>
       <c r="E6" t="n">
         <v>0.8907213668966147</v>
@@ -1058,10 +1058,10 @@
         <v>0.6694906101697025</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6653367155336729</v>
+        <v>0.6648810396122515</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6753814762306477</v>
+        <v>0.6743456739929554</v>
       </c>
       <c r="E7" t="n">
         <v>0.8889396500525378</v>
@@ -1092,10 +1092,10 @@
         <v>0.6393012462396366</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6334666027974618</v>
+        <v>0.6311937574365594</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6449712272508923</v>
+        <v>0.6445851454867498</v>
       </c>
       <c r="E8" t="n">
         <v>0.8894421855726621</v>
@@ -1126,10 +1126,10 @@
         <v>0.6816554136403232</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6736142674362302</v>
+        <v>0.6771999124404189</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6880088945751995</v>
+        <v>0.6882644314391682</v>
       </c>
       <c r="E9" t="n">
         <v>0.8897695950781975</v>
@@ -1160,10 +1160,10 @@
         <v>0.6412644340740697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6333387658007248</v>
+        <v>0.6365977379507634</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6465523695049282</v>
+        <v>0.6493238032474071</v>
       </c>
       <c r="E10" t="n">
         <v>0.8897086816818188</v>
@@ -1194,10 +1194,10 @@
         <v>0.6880531288090916</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6835904789853932</v>
+        <v>0.6791509730960978</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6941467338813794</v>
+        <v>0.693338794233523</v>
       </c>
       <c r="E11" t="n">
         <v>0.8905843117547627</v>
@@ -1289,10 +1289,10 @@
         <v>0.6683520329769145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6633387191909417</v>
+        <v>0.661887789179455</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6767314546350981</v>
+        <v>0.6732475442619732</v>
       </c>
       <c r="E2" t="n">
         <v>0.8894497997472094</v>
@@ -1323,10 +1323,10 @@
         <v>0.5276181072228926</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5234790741559303</v>
+        <v>0.5246949288489343</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5318692537428628</v>
+        <v>0.5317978147511441</v>
       </c>
       <c r="E3" t="n">
         <v>0.7993665006776616</v>
@@ -1357,10 +1357,10 @@
         <v>0.6207017990291458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6161420128441838</v>
+        <v>0.6147289760714122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6257118167463771</v>
+        <v>0.6278562074866378</v>
       </c>
       <c r="E4" t="n">
         <v>0.7286079766092558</v>
@@ -1391,10 +1391,10 @@
         <v>0.6839180132070286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6786560570751534</v>
+        <v>0.6785347327117701</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6917452850795786</v>
+        <v>0.6905744518177567</v>
       </c>
       <c r="E5" t="n">
         <v>0.8901655321546591</v>
@@ -1425,10 +1425,10 @@
         <v>0.6906386446636622</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6786327735538328</v>
+        <v>0.6843534345878546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6957681213967954</v>
+        <v>0.6933364761543045</v>
       </c>
       <c r="E6" t="n">
         <v>0.8906985243729727</v>
@@ -1459,10 +1459,10 @@
         <v>0.6682672277361561</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6629540807111258</v>
+        <v>0.6586251901714633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.673140283100336</v>
+        <v>0.6736785723700113</v>
       </c>
       <c r="E7" t="n">
         <v>0.8889548784016325</v>
@@ -1493,10 +1493,10 @@
         <v>0.6390526174831586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.630402750043492</v>
+        <v>0.6321351674403795</v>
       </c>
       <c r="D8" t="n">
-        <v>0.644971218082139</v>
+        <v>0.645608080948742</v>
       </c>
       <c r="E8" t="n">
         <v>0.8894345713981148</v>
@@ -1527,10 +1527,10 @@
         <v>0.6749385878853063</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6656265716067427</v>
+        <v>0.6706319023517928</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6825620813802488</v>
+        <v>0.6823408080478204</v>
       </c>
       <c r="E9" t="n">
         <v>0.8895792407145141</v>
@@ -1561,10 +1561,10 @@
         <v>0.640639606848796</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6351079337407632</v>
+        <v>0.6358584417695486</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6462511237798083</v>
+        <v>0.6462682323818786</v>
       </c>
       <c r="E10" t="n">
         <v>0.8896858391581769</v>
@@ -1595,10 +1595,10 @@
         <v>0.6834934292660211</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6772029850045593</v>
+        <v>0.6790304585884853</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6910649295664915</v>
+        <v>0.690533109281108</v>
       </c>
       <c r="E11" t="n">
         <v>0.8903635006928898</v>
